--- a/webusers.xlsx
+++ b/webusers.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000"/>
+    <workbookView windowWidth="23040" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -92,45 +92,66 @@
     <t>توتال</t>
   </si>
   <si>
+    <t>Fawzia nady</t>
+  </si>
+  <si>
+    <t>مش بتبصم</t>
+  </si>
+  <si>
     <t>موكبير</t>
   </si>
   <si>
-    <t>محمد</t>
+    <t>Mohammad Nasr Mohammad Moussa</t>
+  </si>
+  <si>
+    <t>Farah</t>
+  </si>
+  <si>
+    <t>طارق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وليد على </t>
+  </si>
+  <si>
+    <t>manager</t>
+  </si>
+  <si>
+    <t>Fahd</t>
+  </si>
+  <si>
+    <t>security</t>
+  </si>
+  <si>
+    <t>Mishari</t>
+  </si>
+  <si>
+    <t>بيبصم مش معروف الاسم</t>
+  </si>
+  <si>
+    <t>رحيمه</t>
+  </si>
+  <si>
+    <t>شيماء</t>
+  </si>
+  <si>
+    <t>academy</t>
+  </si>
+  <si>
+    <t>زينب عبدالقادر</t>
+  </si>
+  <si>
+    <t>gym coach</t>
+  </si>
+  <si>
+    <t>امجد لابراهيم عمر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إبراهيم محمد أحمد  تراوري </t>
   </si>
   <si>
     <t>null</t>
   </si>
   <si>
-    <t>طارق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وليد على </t>
-  </si>
-  <si>
-    <t>manager</t>
-  </si>
-  <si>
-    <t>رحيمه</t>
-  </si>
-  <si>
-    <t>شيماء</t>
-  </si>
-  <si>
-    <t>academy</t>
-  </si>
-  <si>
-    <t>زينب عبدالقادر</t>
-  </si>
-  <si>
-    <t>gym coach</t>
-  </si>
-  <si>
-    <t>امجد لابراهيم عمر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إبراهيم محمد أحمد  تراوري </t>
-  </si>
-  <si>
     <t>محمد حسين عمر محمد</t>
   </si>
   <si>
@@ -146,6 +167,9 @@
     <t>swimming coach</t>
   </si>
   <si>
+    <t xml:space="preserve">هاتان </t>
+  </si>
+  <si>
     <t>فايزه</t>
   </si>
   <si>
@@ -257,6 +281,12 @@
     <t>فرحات</t>
   </si>
   <si>
+    <t>يوسف</t>
+  </si>
+  <si>
+    <t>انيس</t>
+  </si>
+  <si>
     <t>ابراهيم مسعد</t>
   </si>
   <si>
@@ -269,7 +299,7 @@
     <t>علياء</t>
   </si>
   <si>
-    <t>Mohammad Nasr Mohammad Moussa</t>
+    <t>Tasin ahmed</t>
   </si>
 </sst>
 </file>
@@ -282,13 +312,25 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -435,7 +477,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,6 +492,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -635,7 +701,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -669,6 +735,21 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -787,137 +868,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -926,6 +1007,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -941,7 +1038,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -980,6 +1077,16 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1246,19 +1353,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="36.5727272727273" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5740740740741" style="1" customWidth="1"/>
     <col min="3" max="3" width="22" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.2909090909091" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.287037037037" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1278,7 +1385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" hidden="1" spans="1:7">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1298,7 +1405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:4">
+    <row r="3" s="1" customFormat="1" hidden="1" spans="1:7">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1312,7 +1419,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" hidden="1" spans="1:7">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1332,7 +1439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" hidden="1" spans="1:7">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1352,27 +1459,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:6">
-      <c r="A6" s="1">
+    <row r="6" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4">
         <v>12</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="4">
         <v>24</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:6">
+    <row r="7" s="1" customFormat="1" hidden="1" spans="1:7">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -1392,960 +1499,957 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:6">
-      <c r="A8" s="1">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="8" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A8" s="4">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4">
+        <v>15</v>
+      </c>
+      <c r="F8" s="4">
         <v>24</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:6">
-      <c r="A9" s="1">
+    <row r="9" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A9" s="4">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4">
         <v>6</v>
       </c>
-      <c r="F9" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:6">
-      <c r="A10" s="1">
+      <c r="F9" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="A10" s="5">
+        <v>12</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A11" s="4">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4">
+        <v>6</v>
+      </c>
+      <c r="F11" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A12" s="1">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A13" s="1">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A14" s="1">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A15" s="1">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A16" s="1">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A17" s="1">
+        <v>21</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:7">
+      <c r="A18" s="5">
+        <v>23</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A19" s="4">
+        <v>26</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4">
+        <v>6</v>
+      </c>
+      <c r="F19" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A20" s="1">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="1">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A21" s="1">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1">
+        <v>17</v>
+      </c>
+      <c r="F21" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A22" s="1">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="1">
+        <v>14</v>
+      </c>
+      <c r="F22" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A23" s="1">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="1">
+        <v>15</v>
+      </c>
+      <c r="F23" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A24" s="1">
+        <v>49</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A25" s="4">
+        <v>53</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="4">
+        <v>15</v>
+      </c>
+      <c r="F25" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A26" s="4">
+        <v>55</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4">
+        <v>15</v>
+      </c>
+      <c r="F26" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A27" s="1">
+        <v>56</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A28" s="1">
+        <v>58</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A29" s="4">
+        <v>61</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="4">
+        <v>6</v>
+      </c>
+      <c r="F29" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:7">
+      <c r="A30" s="5">
+        <v>67</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="5">
+        <v>6</v>
+      </c>
+      <c r="F30" s="5">
+        <v>15</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A31" s="1">
+        <v>70</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A32" s="1">
+        <v>72</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="1">
+        <v>17</v>
+      </c>
+      <c r="F32" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A33" s="1">
+        <v>73</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A34" s="1">
+        <v>77</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8</v>
+      </c>
+      <c r="F34" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:7">
+      <c r="A35" s="5">
+        <v>80</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A36" s="1">
+        <v>82</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="1">
+        <v>12</v>
+      </c>
+      <c r="F36" s="1">
         <v>20</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1">
+    </row>
+    <row r="37" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A37" s="1">
+        <v>86</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="1">
+        <v>17</v>
+      </c>
+      <c r="F37" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A38" s="4">
+        <v>90</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A39" s="1">
+        <v>91</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="1">
+        <v>17</v>
+      </c>
+      <c r="F39" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A40" s="4">
+        <v>92</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="4">
+        <v>15</v>
+      </c>
+      <c r="F40" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" hidden="1" spans="1:7">
+      <c r="A41" s="4">
+        <v>93</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="5">
+        <v>94</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="5">
         <v>6</v>
       </c>
-      <c r="F10" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:4">
-      <c r="A11" s="1">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="F42" s="5">
+        <v>15</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:6">
-      <c r="A12" s="1">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="43" hidden="1" spans="1:7">
+      <c r="A43" s="1">
+        <v>98</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="1">
+        <v>12</v>
+      </c>
+      <c r="F43" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" hidden="1" spans="1:7">
+      <c r="A44" s="1">
+        <v>100</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="1">
+        <v>15</v>
+      </c>
+      <c r="F44" s="1">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:4">
-      <c r="A13" s="1">
-        <v>18</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:6">
-      <c r="A14" s="1">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="1">
-        <v>6</v>
-      </c>
-      <c r="F14" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:6">
-      <c r="A15" s="1">
-        <v>37</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="1">
-        <v>9</v>
-      </c>
-      <c r="F15" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:6">
-      <c r="A16" s="1">
-        <v>39</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="1">
-        <v>17</v>
-      </c>
-      <c r="F16" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:6">
-      <c r="A17" s="1">
-        <v>40</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="1">
-        <v>14</v>
-      </c>
-      <c r="F17" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:6">
-      <c r="A18" s="1">
-        <v>41</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="1">
-        <v>15</v>
-      </c>
-      <c r="F18" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:6">
-      <c r="A19" s="1">
-        <v>49</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="1">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:6">
-      <c r="A20" s="1">
-        <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="1">
-        <v>15</v>
-      </c>
-      <c r="F20" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:6">
-      <c r="A21" s="1">
-        <v>55</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1">
-        <v>15</v>
-      </c>
-      <c r="F21" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:4">
-      <c r="A22" s="1">
-        <v>56</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:6">
-      <c r="A23" s="1">
-        <v>61</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="1">
-        <v>6</v>
-      </c>
-      <c r="F23" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:6">
-      <c r="A24" s="1">
-        <v>67</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="1">
-        <v>6</v>
-      </c>
-      <c r="F24" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:4">
-      <c r="A25" s="1">
-        <v>70</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:6">
-      <c r="A26" s="1">
-        <v>72</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="1">
-        <v>17</v>
-      </c>
-      <c r="F26" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:4">
-      <c r="A27" s="1">
-        <v>73</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:6">
-      <c r="A28" s="1">
-        <v>77</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="1">
-        <v>8</v>
-      </c>
-      <c r="F28" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:4">
-      <c r="A29" s="1">
-        <v>80</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:6">
-      <c r="A30" s="1">
-        <v>82</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="1">
-        <v>12</v>
-      </c>
-      <c r="F30" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:6">
-      <c r="A31" s="1">
-        <v>86</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1">
-        <v>17</v>
-      </c>
-      <c r="F31" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:4">
-      <c r="A32" s="1">
-        <v>90</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:6">
-      <c r="A33" s="1">
-        <v>91</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1">
-        <v>17</v>
-      </c>
-      <c r="F33" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:6">
-      <c r="A34" s="1">
-        <v>92</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="1">
-        <v>15</v>
-      </c>
-      <c r="F34" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:4">
-      <c r="A35" s="1">
-        <v>93</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:6">
-      <c r="A36" s="1">
-        <v>94</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="1">
-        <v>6</v>
-      </c>
-      <c r="F36" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:6">
-      <c r="A37" s="1">
-        <v>98</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="1">
-        <v>12</v>
-      </c>
-      <c r="F37" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:6">
-      <c r="A38" s="1">
-        <v>100</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="1">
-        <v>15</v>
-      </c>
-      <c r="F38" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:4">
-      <c r="A39" s="1">
+    </row>
+    <row r="45" hidden="1" spans="1:7">
+      <c r="A45" s="1">
         <v>101</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:6">
-      <c r="A40" s="1">
-        <v>104</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="1">
-        <v>10</v>
-      </c>
-      <c r="F40" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:6">
-      <c r="A41" s="1">
-        <v>105</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="1">
-        <v>6</v>
-      </c>
-      <c r="F41" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:6">
-      <c r="A42" s="1">
-        <v>106</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="1">
-        <v>8</v>
-      </c>
-      <c r="F42" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="1">
-        <v>107</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="1">
-        <v>109</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" s="1">
-        <v>17</v>
-      </c>
-      <c r="F44" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="1">
-        <v>112</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" hidden="1" spans="1:7">
+      <c r="A46" s="1">
+        <v>104</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="1">
+        <v>10</v>
+      </c>
+      <c r="F46" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" hidden="1" spans="1:7">
+      <c r="A47" s="4">
+        <v>105</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="4">
+        <v>6</v>
+      </c>
+      <c r="F47" s="4">
+        <v>15</v>
+      </c>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" hidden="1" spans="1:7">
+      <c r="A48" s="1">
+        <v>106</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="1">
+        <v>8</v>
+      </c>
+      <c r="F48" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" spans="1:7">
+      <c r="A49" s="4">
+        <v>107</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" hidden="1" spans="1:7">
+      <c r="A50" s="1">
+        <v>109</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="1">
+        <v>17</v>
+      </c>
+      <c r="F50" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" spans="1:7">
+      <c r="A51" s="4">
+        <v>112</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="5">
+        <v>113</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="5">
+        <v>15</v>
+      </c>
+      <c r="F52" s="5">
         <v>22</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="1">
-        <v>113</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="1">
-        <v>15</v>
-      </c>
-      <c r="F46" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="1">
+      <c r="G52" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="5">
         <v>114</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" s="1">
-        <v>15</v>
-      </c>
-      <c r="F47" s="1">
+      <c r="B53" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="5">
+        <v>15</v>
+      </c>
+      <c r="F53" s="5">
         <v>24</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="1">
+      <c r="G53" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="5">
         <v>115</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" s="1">
-        <v>15</v>
-      </c>
-      <c r="F48" s="1">
+      <c r="B54" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="5">
+        <v>15</v>
+      </c>
+      <c r="F54" s="5">
         <v>24</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="1">
+      <c r="G54" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="5">
         <v>116</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="1">
+      <c r="B55" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" hidden="1" spans="1:7">
+      <c r="A56" s="4">
         <v>118</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="1">
+      <c r="B56" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="5">
         <v>120</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="B57" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="5">
         <v>6</v>
       </c>
-      <c r="F51" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="1">
+      <c r="F57" s="5">
+        <v>15</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" hidden="1" spans="1:7">
+      <c r="A58" s="1">
         <v>122</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="1">
-        <v>15</v>
-      </c>
-      <c r="F52" s="1">
+      <c r="B58" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="1">
+        <v>15</v>
+      </c>
+      <c r="F58" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1">
+    <row r="59" hidden="1" spans="1:7">
+      <c r="A59" s="1">
         <v>123</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="1">
-        <v>17</v>
-      </c>
-      <c r="F53" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="1">
-        <v>127</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="1">
-        <v>18</v>
-      </c>
-      <c r="F54" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="1">
-        <v>128</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" s="1">
-        <v>15</v>
-      </c>
-      <c r="F55" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="1">
-        <v>129</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="1">
-        <v>15</v>
-      </c>
-      <c r="F56" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="1">
-        <v>133</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="1">
-        <v>17</v>
-      </c>
-      <c r="F57" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="1">
-        <v>134</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="1">
-        <v>17</v>
-      </c>
-      <c r="F58" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="1">
-        <v>135</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>77</v>
+      <c r="B59" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E59" s="1">
         <v>17</v>
@@ -2354,52 +2458,205 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" hidden="1" spans="1:7">
       <c r="A60" s="1">
+        <v>127</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="1">
+        <v>18</v>
+      </c>
+      <c r="F60" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" hidden="1" spans="1:7">
+      <c r="A61" s="1">
+        <v>128</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="1">
+        <v>15</v>
+      </c>
+      <c r="F61" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="5">
+        <v>129</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="5">
+        <v>15</v>
+      </c>
+      <c r="F62" s="5">
+        <v>22</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="5">
+        <v>131</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="5">
+        <v>132</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" hidden="1" spans="1:6">
+      <c r="A65" s="1">
+        <v>133</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="1">
+        <v>17</v>
+      </c>
+      <c r="F65" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" hidden="1" spans="1:6">
+      <c r="A66" s="1">
+        <v>134</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="1">
+        <v>17</v>
+      </c>
+      <c r="F66" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" hidden="1" spans="1:6">
+      <c r="A67" s="1">
+        <v>135</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="1">
+        <v>17</v>
+      </c>
+      <c r="F67" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="1" spans="1:6">
+      <c r="A68" s="1">
         <v>138</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C60" s="1" t="s">
+      <c r="B68" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="1">
-        <v>15</v>
-      </c>
-      <c r="F60" s="1">
+      <c r="D68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="1">
+        <v>15</v>
+      </c>
+      <c r="F68" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="1">
-        <v>17</v>
-      </c>
-      <c r="F61" s="1">
-        <v>21</v>
-      </c>
+    <row r="69" hidden="1" spans="1:6">
+      <c r="A69" s="7">
+        <v>137</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F61" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:F61">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F69" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <sortState ref="A2:F69">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
-  <sortState ref="A1:F37">
-    <sortCondition ref="C1:C2"/>
+  <sortState ref="A2:F65">
+    <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>

--- a/webusers.xlsx
+++ b/webusers.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10440"/>
+    <workbookView windowWidth="11520" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -477,7 +477,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,12 +505,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -874,7 +868,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -898,16 +892,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -916,89 +910,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1021,10 +1015,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1077,16 +1068,6 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1353,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:G69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
@@ -1385,7 +1366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" spans="1:7">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1405,7 +1386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1419,7 +1400,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1439,7 +1420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1459,7 +1440,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1479,7 +1460,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="7" s="1" customFormat="1" spans="1:7">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -1499,7 +1480,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="8" s="1" customFormat="1" spans="1:7">
       <c r="A8" s="4">
         <v>8</v>
       </c>
@@ -1519,7 +1500,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="9" s="1" customFormat="1" spans="1:7">
       <c r="A9" s="4">
         <v>9</v>
       </c>
@@ -1558,7 +1539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="11" s="1" customFormat="1" spans="1:7">
       <c r="A11" s="4">
         <v>13</v>
       </c>
@@ -1578,7 +1559,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="12" s="1" customFormat="1" spans="1:7">
       <c r="A12" s="1">
         <v>14</v>
       </c>
@@ -1598,7 +1579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="13" s="1" customFormat="1" spans="1:7">
       <c r="A13" s="1">
         <v>16</v>
       </c>
@@ -1609,7 +1590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="14" s="1" customFormat="1" spans="1:7">
       <c r="A14" s="1">
         <v>17</v>
       </c>
@@ -1629,7 +1610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="15" s="1" customFormat="1" spans="1:7">
       <c r="A15" s="1">
         <v>18</v>
       </c>
@@ -1643,7 +1624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="16" s="1" customFormat="1" spans="1:7">
       <c r="A16" s="1">
         <v>19</v>
       </c>
@@ -1654,7 +1635,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="17" s="1" customFormat="1" spans="1:7">
       <c r="A17" s="1">
         <v>21</v>
       </c>
@@ -1677,7 +1658,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="19" s="1" customFormat="1" spans="1:7">
       <c r="A19" s="4">
         <v>26</v>
       </c>
@@ -1697,7 +1678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="20" s="1" customFormat="1" spans="1:7">
       <c r="A20" s="1">
         <v>37</v>
       </c>
@@ -1717,7 +1698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="21" s="1" customFormat="1" spans="1:7">
       <c r="A21" s="1">
         <v>39</v>
       </c>
@@ -1737,7 +1718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="22" s="1" customFormat="1" spans="1:7">
       <c r="A22" s="1">
         <v>40</v>
       </c>
@@ -1757,7 +1738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="23" s="1" customFormat="1" spans="1:7">
       <c r="A23" s="1">
         <v>41</v>
       </c>
@@ -1777,7 +1758,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="24" s="1" customFormat="1" spans="1:7">
       <c r="A24" s="1">
         <v>49</v>
       </c>
@@ -1797,7 +1778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="25" s="1" customFormat="1" spans="1:7">
       <c r="A25" s="4">
         <v>53</v>
       </c>
@@ -1817,7 +1798,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="26" s="1" customFormat="1" spans="1:7">
       <c r="A26" s="4">
         <v>55</v>
       </c>
@@ -1837,7 +1818,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="27" s="1" customFormat="1" spans="1:7">
       <c r="A27" s="1">
         <v>56</v>
       </c>
@@ -1851,7 +1832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="28" s="1" customFormat="1" spans="1:7">
       <c r="A28" s="1">
         <v>58</v>
       </c>
@@ -1859,7 +1840,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="29" s="1" customFormat="1" spans="1:7">
       <c r="A29" s="4">
         <v>61</v>
       </c>
@@ -1902,7 +1883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="31" s="1" customFormat="1" spans="1:7">
       <c r="A31" s="1">
         <v>70</v>
       </c>
@@ -1916,7 +1897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="32" s="1" customFormat="1" spans="1:7">
       <c r="A32" s="1">
         <v>72</v>
       </c>
@@ -1936,7 +1917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="33" s="1" customFormat="1" spans="1:7">
       <c r="A33" s="1">
         <v>73</v>
       </c>
@@ -1950,7 +1931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="34" s="1" customFormat="1" spans="1:7">
       <c r="A34" s="1">
         <v>77</v>
       </c>
@@ -1989,7 +1970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="36" s="1" customFormat="1" spans="1:7">
       <c r="A36" s="1">
         <v>82</v>
       </c>
@@ -2009,7 +1990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="37" s="1" customFormat="1" spans="1:7">
       <c r="A37" s="1">
         <v>86</v>
       </c>
@@ -2029,7 +2010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="38" s="1" customFormat="1" spans="1:7">
       <c r="A38" s="4">
         <v>90</v>
       </c>
@@ -2045,7 +2026,7 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="39" s="1" customFormat="1" spans="1:7">
       <c r="A39" s="1">
         <v>91</v>
       </c>
@@ -2065,7 +2046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="40" s="1" customFormat="1" spans="1:7">
       <c r="A40" s="4">
         <v>92</v>
       </c>
@@ -2085,7 +2066,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" hidden="1" spans="1:7">
+    <row r="41" s="1" customFormat="1" spans="1:7">
       <c r="A41" s="4">
         <v>93</v>
       </c>
@@ -2124,7 +2105,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:7">
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>98</v>
       </c>
@@ -2144,7 +2125,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:7">
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>100</v>
       </c>
@@ -2164,7 +2145,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:7">
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>101</v>
       </c>
@@ -2178,7 +2159,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:7">
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>104</v>
       </c>
@@ -2198,7 +2179,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:7">
+    <row r="47" spans="1:7">
       <c r="A47" s="4">
         <v>105</v>
       </c>
@@ -2219,7 +2200,7 @@
       </c>
       <c r="G47" s="4"/>
     </row>
-    <row r="48" hidden="1" spans="1:7">
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <v>106</v>
       </c>
@@ -2239,7 +2220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:7">
+    <row r="49" spans="1:7">
       <c r="A49" s="4">
         <v>107</v>
       </c>
@@ -2255,7 +2236,7 @@
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
     </row>
-    <row r="50" hidden="1" spans="1:7">
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>109</v>
       </c>
@@ -2275,7 +2256,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:7">
+    <row r="51" spans="1:7">
       <c r="A51" s="4">
         <v>112</v>
       </c>
@@ -2379,7 +2360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:7">
+    <row r="56" spans="1:7">
       <c r="A56" s="4">
         <v>118</v>
       </c>
@@ -2418,7 +2399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:7">
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <v>122</v>
       </c>
@@ -2438,7 +2419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:7">
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <v>123</v>
       </c>
@@ -2458,7 +2439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:7">
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <v>127</v>
       </c>
@@ -2478,7 +2459,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:7">
+    <row r="61" spans="1:7">
       <c r="A61" s="1">
         <v>128</v>
       </c>
@@ -2551,7 +2532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:6">
+    <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>133</v>
       </c>
@@ -2571,7 +2552,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:6">
+    <row r="66" spans="1:6">
       <c r="A66" s="1">
         <v>134</v>
       </c>
@@ -2591,7 +2572,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:6">
+    <row r="67" spans="1:6">
       <c r="A67" s="1">
         <v>135</v>
       </c>
@@ -2611,7 +2592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:6">
+    <row r="68" spans="1:6">
       <c r="A68" s="1">
         <v>138</v>
       </c>
@@ -2631,14 +2612,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:6">
+    <row r="69" spans="1:6">
       <c r="A69" s="7">
         <v>137</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D69" s="7"/>
@@ -2647,10 +2628,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F69" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
-    <sortState ref="A2:F69">
+    <sortState ref="A1:F69">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>

--- a/webusers.xlsx
+++ b/webusers.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="10440"/>
+    <workbookView windowWidth="20496" windowHeight="7560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1634,6 +1634,12 @@
       <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="E16" s="1">
+        <v>12</v>
+      </c>
+      <c r="F16" s="1">
+        <v>21</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:7">
       <c r="A17" s="1">
